--- a/data/hex_xlsx/RAP1V.HE.xlsx
+++ b/data/hex_xlsx/RAP1V.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="530">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -976,6 +976,9 @@
   </si>
   <si>
     <t>Other Interest-Bearing</t>
+  </si>
+  <si>
+    <t>Interest-Bearing (not use)</t>
   </si>
   <si>
     <t>Commercial Paper</t>
@@ -1737,7 +1740,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1818,6 +1821,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -14548,22 +14554,46 @@
       <c r="K83" s="15">
         <v>328.7</v>
       </c>
-      <c r="L83" s="19"/>
-      <c r="M83" s="19"/>
-      <c r="N83" s="19"/>
-      <c r="O83" s="19"/>
-      <c r="P83" s="19"/>
+      <c r="L83" s="15">
+        <f t="shared" ref="L83:O83" si="1">L84+L86+L90+L94+L98</f>
+        <v>324.48</v>
+      </c>
+      <c r="M83" s="15">
+        <f t="shared" si="1"/>
+        <v>289.24</v>
+      </c>
+      <c r="N83" s="15">
+        <f t="shared" si="1"/>
+        <v>255.15</v>
+      </c>
+      <c r="O83" s="15">
+        <f t="shared" si="1"/>
+        <v>215.79</v>
+      </c>
+      <c r="P83" s="15">
+        <v>220.5</v>
+      </c>
       <c r="Q83" s="15">
         <v>223.51</v>
       </c>
       <c r="R83" s="15">
         <v>228.08</v>
       </c>
-      <c r="S83" s="19"/>
-      <c r="T83" s="19"/>
-      <c r="U83" s="19"/>
-      <c r="V83" s="19"/>
-      <c r="W83" s="19"/>
+      <c r="S83" s="15">
+        <v>278.62</v>
+      </c>
+      <c r="T83" s="15">
+        <v>225.17</v>
+      </c>
+      <c r="U83" s="15">
+        <v>241.81</v>
+      </c>
+      <c r="V83" s="15">
+        <v>237.93</v>
+      </c>
+      <c r="W83" s="15">
+        <v>244.66</v>
+      </c>
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
@@ -16652,12 +16682,24 @@
       <c r="A127" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
+      <c r="B127" s="15">
+        <v>218.56</v>
+      </c>
+      <c r="C127" s="15">
+        <v>263.58</v>
+      </c>
+      <c r="D127" s="15">
+        <v>242.72</v>
+      </c>
+      <c r="E127" s="15">
+        <v>973.99</v>
+      </c>
+      <c r="F127" s="15">
+        <v>430.49</v>
+      </c>
+      <c r="G127" s="15">
+        <v>158.19</v>
+      </c>
       <c r="H127" s="15">
         <v>347.37</v>
       </c>
@@ -16682,18 +16724,36 @@
       <c r="O127" s="15">
         <v>407.36</v>
       </c>
-      <c r="P127" s="19"/>
+      <c r="P127" s="15">
+        <f>SUM(P128:P133)</f>
+        <v>897.45</v>
+      </c>
       <c r="Q127" s="15">
         <v>736.73</v>
       </c>
       <c r="R127" s="15">
         <v>605.45</v>
       </c>
-      <c r="S127" s="19"/>
-      <c r="T127" s="19"/>
-      <c r="U127" s="19"/>
-      <c r="V127" s="19"/>
-      <c r="W127" s="19"/>
+      <c r="S127" s="15">
+        <f t="shared" ref="S127:W127" si="2">SUM(S128:S133)</f>
+        <v>756.26</v>
+      </c>
+      <c r="T127" s="15">
+        <f t="shared" si="2"/>
+        <v>456.69</v>
+      </c>
+      <c r="U127" s="15">
+        <f t="shared" si="2"/>
+        <v>485.26</v>
+      </c>
+      <c r="V127" s="15">
+        <f t="shared" si="2"/>
+        <v>443.13</v>
+      </c>
+      <c r="W127" s="15">
+        <f t="shared" si="2"/>
+        <v>548.64</v>
+      </c>
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
@@ -16768,8 +16828,8 @@
       <c r="W129" s="19"/>
     </row>
     <row r="130" ht="15.0" customHeight="1">
-      <c r="A130" s="14" t="s">
-        <v>316</v>
+      <c r="A130" s="27" t="s">
+        <v>319</v>
       </c>
       <c r="B130" s="15">
         <v>218.56</v>
@@ -16808,7 +16868,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B131" s="19"/>
       <c r="C131" s="15">
@@ -16865,7 +16925,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B132" s="19"/>
       <c r="C132" s="20">
@@ -16920,7 +16980,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B133" s="19"/>
       <c r="C133" s="20">
@@ -16985,7 +17045,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="20">
@@ -17018,7 +17078,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B135" s="20">
         <v>50.8</v>
@@ -17079,7 +17139,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B136" s="19"/>
       <c r="C136" s="15">
@@ -17118,7 +17178,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B137" s="19"/>
       <c r="C137" s="15">
@@ -17183,7 +17243,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B138" s="19"/>
       <c r="C138" s="20">
@@ -17297,7 +17357,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="20">
@@ -17362,7 +17422,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B141" s="19"/>
       <c r="C141" s="20">
@@ -17427,7 +17487,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B142" s="19"/>
       <c r="C142" s="19"/>
@@ -17468,7 +17528,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B143" s="19"/>
       <c r="C143" s="20">
@@ -17501,7 +17561,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B144" s="15">
         <v>446.57</v>
@@ -17560,7 +17620,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B145" s="19"/>
       <c r="C145" s="19"/>
@@ -17601,7 +17661,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B146" s="19"/>
       <c r="C146" s="19"/>
@@ -17630,7 +17690,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B147" s="19"/>
       <c r="C147" s="19"/>
@@ -17667,7 +17727,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B148" s="19"/>
       <c r="C148" s="20">
@@ -17720,7 +17780,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B149" s="19"/>
       <c r="C149" s="20">
@@ -17857,7 +17917,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="17">
         <v>715.93</v>
@@ -17928,7 +17988,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B153" s="19"/>
       <c r="C153" s="19"/>
@@ -17957,7 +18017,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B154" s="19"/>
       <c r="C154" s="19"/>
@@ -17990,7 +18050,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B155" s="15">
         <v>750.19</v>
@@ -18061,7 +18121,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B156" s="19"/>
       <c r="C156" s="15">
@@ -18116,7 +18176,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B157" s="19"/>
       <c r="C157" s="19"/>
@@ -18147,7 +18207,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B158" s="19"/>
       <c r="C158" s="19"/>
@@ -18176,7 +18236,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B159" s="20">
         <v>66.16</v>
@@ -18239,7 +18299,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B160" s="15">
         <v>128.77</v>
@@ -18351,7 +18411,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B162" s="19"/>
       <c r="C162" s="19"/>
@@ -18398,7 +18458,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B163" s="19"/>
       <c r="C163" s="19"/>
@@ -18429,7 +18489,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B164" s="19"/>
       <c r="C164" s="20">
@@ -18494,7 +18554,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
@@ -18533,7 +18593,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B166" s="19"/>
       <c r="C166" s="19"/>
@@ -18603,7 +18663,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B168" s="19"/>
       <c r="C168" s="15">
@@ -18668,7 +18728,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B169" s="19"/>
       <c r="C169" s="19"/>
@@ -18699,7 +18759,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B170" s="19"/>
       <c r="C170" s="19"/>
@@ -18730,7 +18790,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B171" s="19"/>
       <c r="C171" s="20">
@@ -18767,7 +18827,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B172" s="17">
         <v>945.12</v>
@@ -18838,7 +18898,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B173" s="17">
         <v>1661.05</v>
@@ -18909,7 +18969,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B174" s="19"/>
       <c r="C174" s="19"/>
@@ -18938,7 +18998,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B175" s="21">
         <v>-161.85</v>
@@ -18987,7 +19047,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B176" s="20">
         <v>42.53</v>
@@ -19054,7 +19114,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B177" s="15">
         <v>197.29</v>
@@ -19121,7 +19181,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B178" s="19"/>
       <c r="C178" s="19"/>
@@ -19174,7 +19234,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B179" s="20">
         <v>57.89</v>
@@ -19237,7 +19297,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B180" s="18">
         <v>-47.26</v>
@@ -19254,7 +19314,7 @@
       <c r="F180" s="18">
         <v>-25.03</v>
       </c>
-      <c r="G180" s="27">
+      <c r="G180" s="28">
         <v>0.0</v>
       </c>
       <c r="H180" s="19"/>
@@ -19298,7 +19358,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B181" s="15">
         <v>1227.48</v>
@@ -19365,7 +19425,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="19"/>
@@ -19437,7 +19497,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B184" s="19"/>
       <c r="C184" s="19"/>
@@ -19476,7 +19536,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B185" s="15">
         <v>295.35</v>
@@ -19519,7 +19579,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B186" s="19"/>
       <c r="C186" s="19"/>
@@ -19552,7 +19612,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B187" s="17">
         <v>1611.43</v>
@@ -19686,7 +19746,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B189" s="26"/>
       <c r="C189" s="26"/>
@@ -19749,7 +19809,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B190" s="19"/>
       <c r="C190" s="19"/>
@@ -19780,7 +19840,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B191" s="17">
         <v>1611.43</v>
@@ -19851,7 +19911,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B192" s="18">
         <v>-1.18</v>
@@ -19892,7 +19952,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B193" s="17">
         <v>3271.3</v>
@@ -19963,7 +20023,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B194" s="20">
         <v>38.13</v>
@@ -20034,7 +20094,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B195" s="20">
         <v>39.0</v>
@@ -20105,7 +20165,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B196" s="20">
         <v>0.87</v>
@@ -20176,7 +20236,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B197" s="19"/>
       <c r="C197" s="19"/>
@@ -20205,7 +20265,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B198" s="19"/>
       <c r="C198" s="19"/>
@@ -20234,7 +20294,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B199" s="19"/>
       <c r="C199" s="19"/>
@@ -20289,7 +20349,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B200" s="19"/>
       <c r="C200" s="19"/>
@@ -20344,7 +20404,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B201" s="19"/>
       <c r="C201" s="19"/>
@@ -20377,7 +20437,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B202" s="19"/>
       <c r="C202" s="19"/>
@@ -20418,7 +20478,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B203" s="19"/>
       <c r="C203" s="19"/>
@@ -20469,7 +20529,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B204" s="19"/>
       <c r="C204" s="19"/>
@@ -20502,7 +20562,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B205" s="19"/>
       <c r="C205" s="19"/>
@@ -20531,7 +20591,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B206" s="19"/>
       <c r="C206" s="19"/>
@@ -20568,7 +20628,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B207" s="19"/>
       <c r="C207" s="15">
@@ -20621,7 +20681,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B208" s="19"/>
       <c r="C208" s="15">
@@ -20674,7 +20734,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B209" s="19"/>
       <c r="C209" s="19"/>
@@ -20721,7 +20781,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B210" s="19"/>
       <c r="C210" s="19"/>
@@ -20756,7 +20816,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B211" s="19"/>
       <c r="C211" s="19"/>
@@ -20805,7 +20865,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B212" s="19"/>
       <c r="C212" s="19"/>
@@ -20850,7 +20910,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B213" s="19"/>
       <c r="C213" s="19"/>
@@ -20879,7 +20939,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B214" s="19"/>
       <c r="C214" s="19"/>
@@ -20916,7 +20976,7 @@
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B215" s="20">
         <v>38.13</v>
@@ -20987,7 +21047,7 @@
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B216" s="20">
         <v>39.0</v>
@@ -21058,7 +21118,7 @@
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B217" s="20">
         <v>0.87</v>
@@ -21129,7 +21189,7 @@
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B218" s="20">
         <v>1.0</v>
@@ -22001,7 +22061,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22387,70 +22447,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -22526,7 +22586,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22695,7 +22755,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B21" s="15">
         <v>303.1</v>
@@ -22878,7 +22938,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="15">
@@ -22945,7 +23005,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -22992,7 +23052,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="20">
@@ -23059,7 +23119,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19">
@@ -23120,7 +23180,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="18">
@@ -23173,7 +23233,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="18">
@@ -23234,7 +23294,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -23271,7 +23331,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="20">
@@ -23312,7 +23372,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B32" s="21">
         <v>-106.49</v>
@@ -23365,7 +23425,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="18">
@@ -23432,7 +23492,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="20">
@@ -23499,7 +23559,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="18">
@@ -23566,7 +23626,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="18">
@@ -23625,7 +23685,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20">
@@ -23662,7 +23722,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B38" s="18">
         <v>-73.73</v>
@@ -23713,7 +23773,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="20">
@@ -23780,7 +23840,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20">
@@ -23847,7 +23907,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="15">
@@ -23914,7 +23974,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -23984,7 +24044,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -24052,7 +24112,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" s="23">
         <v>64.36</v>
@@ -24123,7 +24183,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B47" s="18">
         <v>-50.32</v>
@@ -24166,7 +24226,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="18">
@@ -24233,7 +24293,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="18">
@@ -24300,7 +24360,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" s="20">
         <v>18.72</v>
@@ -24371,7 +24431,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B51" s="19">
         <v>0.0</v>
@@ -24426,7 +24486,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -24457,7 +24517,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -24496,7 +24556,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -24539,7 +24599,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -24570,7 +24630,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
@@ -24605,7 +24665,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -24634,7 +24694,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="20">
@@ -24667,7 +24727,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -24698,7 +24758,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="18">
@@ -24770,7 +24830,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
@@ -24799,7 +24859,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
@@ -24856,7 +24916,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -24885,7 +24945,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -24947,7 +25007,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" s="25">
         <v>-31.6</v>
@@ -25018,7 +25078,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68" s="19"/>
       <c r="C68" s="19">
@@ -25051,7 +25111,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -25112,7 +25172,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
@@ -25155,7 +25215,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B71" s="15">
         <v>111.17</v>
@@ -25190,7 +25250,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B72" s="18">
         <v>-11.7</v>
@@ -25245,7 +25305,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B73" s="21">
         <v>-119.37</v>
@@ -25290,7 +25350,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
@@ -25364,7 +25424,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B76" s="19"/>
       <c r="C76" s="15">
@@ -25425,7 +25485,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" s="18">
         <v>-70.22</v>
@@ -25486,7 +25546,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B78" s="19"/>
       <c r="C78" s="21">
@@ -25547,7 +25607,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
@@ -25592,7 +25652,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
@@ -25629,7 +25689,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -25666,7 +25726,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -25699,7 +25759,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
@@ -25732,7 +25792,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
@@ -25767,7 +25827,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B85" s="19"/>
       <c r="C85" s="19">
@@ -25810,7 +25870,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -25882,7 +25942,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B88" s="25">
         <v>-88.94</v>
@@ -25988,7 +26048,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B90" s="18">
         <v>-57.34</v>
@@ -26039,7 +26099,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B91" s="15">
         <v>256.36</v>
@@ -26110,7 +26170,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B92" s="15">
         <v>215.01</v>
@@ -26181,7 +26241,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B93" s="20">
         <v>16.38</v>
@@ -26281,7 +26341,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="16" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B95" s="25">
         <v>-39.79</v>
@@ -27276,7 +27336,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -27446,22 +27506,22 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -27894,7 +27954,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -27992,3273 +28052,3273 @@
         <v>70</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>478</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>479</v>
+      </c>
+      <c r="B21" s="32">
         <v>1614.25</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>2221.35</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>3321.42</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>4186.6</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>2384.8</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>1919.21</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>1926.55</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>2014.02</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>2413.22</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>2921.86</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>2665.48</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>2636.81</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>2160.27</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <v>2540.71</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>2896.71</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>2319.44</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="32">
         <v>2223.65</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>2339.84</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>2784.8</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>2648.72</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>2481.27</v>
       </c>
-      <c r="W21" s="32"/>
-      <c r="X21" s="31">
+      <c r="W21" s="33"/>
+      <c r="X21" s="32">
         <v>1881.52</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>2384.54</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>2346.86</v>
       </c>
-      <c r="AA21" s="31">
+      <c r="AA21" s="32">
         <v>2623.56</v>
       </c>
-      <c r="AB21" s="32"/>
+      <c r="AB21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
-        <v>479</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="A22" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="B22" s="32">
         <v>3055.65</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>3033.94</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>2835.16</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>2482.59</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>2278.49</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>2291.24</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>2504.74</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>2728.73</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>2679.68</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>2953.36</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>2902.93</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>2652.46</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <v>2206.91</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>2327.46</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>2358.72</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>2445.26</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>2904.08</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>2225.76</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>2238.23</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>2108.99</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>2101.15</v>
       </c>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
+      <c r="A23" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="A24" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="B24" s="32">
         <v>878.81</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>1308.65</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>2044.43</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>3404.7</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>1781.37</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>1063.08</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>1178.52</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>1278.59</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>1462.53</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>1774.66</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>1660.35</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>1711.28</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>1405.0</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <v>1725.26</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <v>2108.59</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="32">
         <v>1626.9</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>1333.41</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>1697.62</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>1963.96</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>1875.04</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>1800.0</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>1717.52</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>1106.53</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>1289.08</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>1471.52</v>
       </c>
-      <c r="AA24" s="31">
+      <c r="AA24" s="32">
         <v>1834.21</v>
       </c>
-      <c r="AB24" s="32"/>
+      <c r="AB24" s="33"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>481</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="A25" s="31" t="s">
+        <v>482</v>
+      </c>
+      <c r="B25" s="32">
         <v>2110.53</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>2080.75</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>1954.48</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>1735.93</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>1441.44</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>1383.15</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>1542.51</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>1702.67</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>1682.14</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>1897.36</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>1941.73</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <v>1811.98</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>1495.39</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>1611.35</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>1646.6</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>1694.01</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>2026.27</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>1684.12</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>1638.75</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>1467.33</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>1422.81</v>
       </c>
-      <c r="W25" s="31">
+      <c r="W25" s="32">
         <v>1426.46</v>
       </c>
-      <c r="X25" s="32"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="32"/>
-      <c r="AA25" s="32"/>
-      <c r="AB25" s="32"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>482</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="B27" s="34">
         <v>22.53</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>33.56</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>52.42</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>87.3</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>45.68</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>27.26</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>30.22</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>32.78</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>37.5</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>45.5</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>42.57</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>43.36</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>35.6</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>43.71</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>53.42</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>41.22</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>33.78</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>44.0</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>50.91</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>48.7</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>47.94</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="34">
         <v>45.75</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="34">
         <v>29.47</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="34">
         <v>34.34</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="34">
         <v>46.72</v>
       </c>
-      <c r="AA27" s="33">
+      <c r="AA27" s="34">
         <v>58.23</v>
       </c>
-      <c r="AB27" s="32"/>
+      <c r="AB27" s="33"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
-        <v>484</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="B28" s="34">
         <v>54.12</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>53.35</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>50.11</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>44.51</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>36.96</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>35.47</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>39.55</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>43.54</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>42.91</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>48.29</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>49.3</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>45.91</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>37.89</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>41.02</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>42.13</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>43.61</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>52.7</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>44.1</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="34">
         <v>43.11</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="34">
         <v>38.84</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="34">
         <v>39.41</v>
       </c>
-      <c r="W28" s="33">
+      <c r="W28" s="34">
         <v>39.54</v>
       </c>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
+      <c r="A29" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>486</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="B30" s="35">
         <v>25.79</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>9.52</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>-12.51</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>3.03</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>22.31</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>19.09</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>0.26</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>10.27</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="35">
         <v>11.56</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="35">
         <v>3.57</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>11.96</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>2.34</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <v>9.28</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>3.09</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>2.54</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>9.19</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>-0.51</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>5.3</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>1.17</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>2.73</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>1.33</v>
       </c>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34">
+      <c r="W30" s="35"/>
+      <c r="X30" s="35">
         <v>20.44</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="36">
         <v>-1.43</v>
       </c>
-      <c r="Z30" s="34">
+      <c r="Z30" s="35">
         <v>4.14</v>
       </c>
-      <c r="AA30" s="34">
+      <c r="AA30" s="35">
         <v>3.14</v>
       </c>
-      <c r="AB30" s="34"/>
+      <c r="AB30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
-        <v>487</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="A31" s="31" t="s">
+        <v>488</v>
+      </c>
+      <c r="B31" s="35">
         <v>6.05</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>5.98</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>4.8</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>9.52</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>13.2</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>8.46</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>7.82</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>7.57</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>7.54</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>5.88</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <v>5.44</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>5.0</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <v>4.8</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>4.08</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>3.62</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>3.7</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <v>2.18</v>
       </c>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
+      <c r="A32" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="B33" s="34">
+      <c r="A33" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="B33" s="35">
         <v>0.0</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>1.33</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>3.0</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>0.0</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>0.0</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>2.17</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>1.31</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>3.0</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>3.63</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>4.22</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>5.1</v>
       </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34">
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35">
         <v>3.27</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <v>2.23</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <v>3.07</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <v>4.16</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="35">
         <v>1.74</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="35">
         <v>1.43</v>
       </c>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34">
+      <c r="U33" s="35"/>
+      <c r="V33" s="35">
         <v>1.55</v>
       </c>
-      <c r="W33" s="34">
+      <c r="W33" s="35">
         <v>2.2</v>
       </c>
-      <c r="X33" s="34">
+      <c r="X33" s="35">
         <v>0.51</v>
       </c>
-      <c r="Y33" s="34">
+      <c r="Y33" s="35">
         <v>0.47</v>
       </c>
-      <c r="Z33" s="34">
+      <c r="Z33" s="35">
         <v>0.3</v>
       </c>
-      <c r="AA33" s="34">
+      <c r="AA33" s="35">
         <v>0.0</v>
       </c>
-      <c r="AB33" s="34"/>
+      <c r="AB33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>490</v>
-      </c>
-      <c r="B34" s="34">
+      <c r="A34" s="31" t="s">
+        <v>491</v>
+      </c>
+      <c r="B34" s="35">
         <v>0.83</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>1.05</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>1.05</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>0.9</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>1.98</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>3.05</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>3.66</v>
       </c>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34">
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35">
         <v>2.76</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="35">
         <v>2.35</v>
       </c>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34">
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35">
         <v>1.27</v>
       </c>
-      <c r="W34" s="34">
+      <c r="W34" s="35">
         <v>0.96</v>
       </c>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="35"/>
+      <c r="AB34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="B35" s="34">
+      <c r="A35" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="B35" s="35">
         <v>0.0</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>1.33</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>3.0</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>0.0</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>0.0</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>2.17</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>1.31</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>3.0</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>3.63</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>4.22</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>5.1</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>4.42</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>4.74</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>4.07</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>2.77</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <v>3.82</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <v>5.17</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="35">
         <v>2.16</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="35">
         <v>1.78</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="35">
         <v>1.48</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="35">
         <v>2.06</v>
       </c>
-      <c r="W35" s="34">
+      <c r="W35" s="35">
         <v>0.0</v>
       </c>
-      <c r="X35" s="34">
+      <c r="X35" s="35">
         <v>0.51</v>
       </c>
-      <c r="Y35" s="34">
+      <c r="Y35" s="35">
         <v>0.47</v>
       </c>
-      <c r="Z35" s="34">
+      <c r="Z35" s="35">
         <v>0.3</v>
       </c>
-      <c r="AA35" s="34">
+      <c r="AA35" s="35">
         <v>0.0</v>
       </c>
-      <c r="AB35" s="34"/>
+      <c r="AB35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>492</v>
-      </c>
-      <c r="B36" s="34">
+      <c r="A36" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="B36" s="35">
         <v>0.83</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>1.05</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>1.05</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>0.9</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>1.98</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>3.05</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>3.66</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>4.16</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="35">
         <v>4.44</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <v>4.49</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <v>4.11</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>3.89</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <v>3.95</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="35">
         <v>3.43</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="35">
         <v>2.92</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <v>2.62</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <v>2.28</v>
       </c>
-      <c r="S36" s="34">
+      <c r="S36" s="35">
         <v>1.51</v>
       </c>
-      <c r="T36" s="34">
+      <c r="T36" s="35">
         <v>1.34</v>
       </c>
-      <c r="U36" s="34">
+      <c r="U36" s="35">
         <v>1.1</v>
       </c>
-      <c r="V36" s="34">
+      <c r="V36" s="35">
         <v>0.89</v>
       </c>
-      <c r="W36" s="34">
+      <c r="W36" s="35">
         <v>0.45</v>
       </c>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="B38" s="34">
         <v>0.59</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>0.92</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.4</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>2.44</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.49</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>0.88</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.0</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.15</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>1.24</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>1.38</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>1.41</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>1.63</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>1.47</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>1.71</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>2.19</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>1.81</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>1.34</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>2.28</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>2.96</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>3.12</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>3.68</v>
       </c>
-      <c r="W38" s="32"/>
-      <c r="X38" s="33">
+      <c r="W38" s="33"/>
+      <c r="X38" s="34">
         <v>3.15</v>
       </c>
-      <c r="Y38" s="33">
+      <c r="Y38" s="34">
         <v>4.28</v>
       </c>
-      <c r="Z38" s="33">
+      <c r="Z38" s="34">
         <v>8.0</v>
       </c>
-      <c r="AA38" s="33">
+      <c r="AA38" s="34">
         <v>17.69</v>
       </c>
-      <c r="AB38" s="32"/>
+      <c r="AB38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
-        <v>495</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="B39" s="34">
         <v>1.39</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.45</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.47</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.42</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.15</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.14</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>1.24</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>1.37</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>1.42</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>1.52</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>1.68</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>1.76</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>1.71</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>1.87</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>2.08</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>2.22</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>2.55</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="34">
         <v>2.9</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="34">
         <v>3.12</v>
       </c>
-      <c r="U39" s="33">
+      <c r="U39" s="34">
         <v>3.33</v>
       </c>
-      <c r="V39" s="33">
+      <c r="V39" s="34">
         <v>3.94</v>
       </c>
-      <c r="W39" s="32"/>
-      <c r="X39" s="32"/>
-      <c r="Y39" s="32"/>
-      <c r="Z39" s="32"/>
-      <c r="AA39" s="32"/>
-      <c r="AB39" s="32"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="33"/>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
+      <c r="A40" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B41" s="34">
         <v>3.55</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>4.76</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>3.58</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>5.81</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>4.04</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>2.3</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>2.75</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>3.4</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>3.21</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>3.41</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>3.35</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>3.78</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>3.38</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>3.62</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>4.95</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>3.95</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>3.1</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>3.84</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>8.71</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>11.63</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>14.57</v>
       </c>
-      <c r="W41" s="32"/>
-      <c r="X41" s="32"/>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="32"/>
-      <c r="AA41" s="32"/>
-      <c r="AB41" s="32"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="33"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>498</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="B42" s="34">
         <v>4.47</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>4.1</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>3.8</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>3.78</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>3.12</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>3.02</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>3.24</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>3.44</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>3.43</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>3.51</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>3.81</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>3.93</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>3.82</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>3.91</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>4.57</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>5.2</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>6.46</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="34">
         <v>6.05</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="34">
         <v>8.83</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="34">
         <v>14.99</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="34">
         <v>63.85</v>
       </c>
-      <c r="W42" s="32"/>
-      <c r="X42" s="32"/>
-      <c r="Y42" s="32"/>
-      <c r="Z42" s="32"/>
-      <c r="AA42" s="32"/>
-      <c r="AB42" s="32"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="33"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>500</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="B44" s="34">
         <v>0.34</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>0.53</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>0.71</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>1.16</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>0.64</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>0.39</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>0.45</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>0.5</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>0.61</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>0.65</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>0.66</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>0.7</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>0.65</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>0.79</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>0.99</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>0.83</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>0.56</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>0.89</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>1.05</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>1.18</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>1.26</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="34">
         <v>1.28</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="34">
         <v>0.78</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>0.95</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="34">
         <v>1.53</v>
       </c>
-      <c r="AA44" s="33">
+      <c r="AA44" s="34">
         <v>2.2</v>
       </c>
-      <c r="AB44" s="32"/>
+      <c r="AB44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
-        <v>501</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="B45" s="34">
         <v>0.7</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>0.7</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>0.68</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>0.64</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>0.52</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>0.52</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>0.58</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>0.63</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>0.66</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>0.69</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>0.76</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>0.79</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>0.77</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>0.82</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>0.87</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>0.89</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>0.97</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="34">
         <v>1.11</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="34">
         <v>1.13</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="34">
         <v>1.08</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>1.03</v>
       </c>
-      <c r="W45" s="33">
+      <c r="W45" s="34">
         <v>1.07</v>
       </c>
-      <c r="X45" s="32"/>
-      <c r="Y45" s="32"/>
-      <c r="Z45" s="32"/>
-      <c r="AA45" s="32"/>
-      <c r="AB45" s="32"/>
+      <c r="X45" s="33"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
+      <c r="A46" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="B47" s="33">
+      <c r="A47" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="B47" s="34">
         <v>3.88</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="34">
         <v>10.51</v>
       </c>
-      <c r="D47" s="32"/>
-      <c r="E47" s="33">
+      <c r="D47" s="33"/>
+      <c r="E47" s="34">
         <v>33.02</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="34">
         <v>4.48</v>
       </c>
-      <c r="G47" s="33">
+      <c r="G47" s="34">
         <v>5.24</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <v>389.62</v>
       </c>
-      <c r="I47" s="33">
+      <c r="I47" s="34">
         <v>9.74</v>
       </c>
-      <c r="J47" s="33">
+      <c r="J47" s="34">
         <v>8.65</v>
       </c>
-      <c r="K47" s="33">
+      <c r="K47" s="34">
         <v>27.98</v>
       </c>
-      <c r="L47" s="33">
+      <c r="L47" s="34">
         <v>8.36</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="34">
         <v>42.77</v>
       </c>
-      <c r="N47" s="33">
+      <c r="N47" s="34">
         <v>10.78</v>
       </c>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <v>32.34</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="34">
         <v>39.38</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="Q47" s="34">
         <v>10.89</v>
       </c>
-      <c r="R47" s="32"/>
-      <c r="S47" s="33">
+      <c r="R47" s="33"/>
+      <c r="S47" s="34">
         <v>18.88</v>
       </c>
-      <c r="T47" s="33">
+      <c r="T47" s="34">
         <v>85.35</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="34">
         <v>36.69</v>
       </c>
-      <c r="V47" s="33">
+      <c r="V47" s="34">
         <v>75.38</v>
       </c>
-      <c r="W47" s="32"/>
-      <c r="X47" s="33">
+      <c r="W47" s="33"/>
+      <c r="X47" s="34">
         <v>4.89</v>
       </c>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="33">
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="34">
         <v>24.18</v>
       </c>
-      <c r="AA47" s="33">
+      <c r="AA47" s="34">
         <v>31.8</v>
       </c>
-      <c r="AB47" s="32"/>
+      <c r="AB47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>504</v>
-      </c>
-      <c r="B48" s="33">
+      <c r="A48" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="B48" s="34">
         <v>16.54</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>16.73</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <v>20.82</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <v>10.51</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <v>7.57</v>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <v>11.81</v>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="34">
         <v>12.79</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="34">
         <v>13.21</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="34">
         <v>13.26</v>
       </c>
-      <c r="K48" s="33">
+      <c r="K48" s="34">
         <v>17.0</v>
       </c>
-      <c r="L48" s="33">
+      <c r="L48" s="34">
         <v>18.38</v>
       </c>
-      <c r="M48" s="33">
+      <c r="M48" s="34">
         <v>19.99</v>
       </c>
-      <c r="N48" s="33">
+      <c r="N48" s="34">
         <v>20.85</v>
       </c>
-      <c r="O48" s="33">
+      <c r="O48" s="34">
         <v>24.51</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="34">
         <v>27.62</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="34">
         <v>27.06</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="34">
         <v>45.83</v>
       </c>
-      <c r="S48" s="32"/>
-      <c r="T48" s="32"/>
-      <c r="U48" s="32"/>
-      <c r="V48" s="32"/>
-      <c r="W48" s="32"/>
-      <c r="X48" s="32"/>
-      <c r="Y48" s="32"/>
-      <c r="Z48" s="32"/>
-      <c r="AA48" s="32"/>
-      <c r="AB48" s="32"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="33"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="33"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>506</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="B50" s="34">
         <v>5.77</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>27.12</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>13.64</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>11.49</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>10.37</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>6.44</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>8.99</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>13.72</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="34">
         <v>32.31</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="34">
         <v>12.21</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="34">
         <v>10.8</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="34">
         <v>0.03</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="34">
         <v>9.11</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>9.09</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>9.99</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="34">
         <v>7.73</v>
       </c>
-      <c r="R50" s="33">
+      <c r="R50" s="34">
         <v>5.38</v>
       </c>
-      <c r="S50" s="33">
+      <c r="S50" s="34">
         <v>8.97</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>13.81</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>11.73</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>12.78</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="34">
         <v>22.46</v>
       </c>
-      <c r="X50" s="33">
+      <c r="X50" s="34">
         <v>6.52</v>
       </c>
-      <c r="Y50" s="33">
+      <c r="Y50" s="34">
         <v>12.81</v>
       </c>
-      <c r="Z50" s="33">
+      <c r="Z50" s="34">
         <v>16.14</v>
       </c>
-      <c r="AA50" s="33">
+      <c r="AA50" s="34">
         <v>24.23</v>
       </c>
-      <c r="AB50" s="32"/>
+      <c r="AB50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
-        <v>507</v>
-      </c>
-      <c r="B51" s="33">
+      <c r="A51" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="B51" s="34">
         <v>11.56</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>11.43</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>10.32</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>10.15</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>11.31</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>11.79</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>13.01</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>0.13</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="34">
         <v>0.14</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="34">
         <v>0.15</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="34">
         <v>0.16</v>
       </c>
-      <c r="M51" s="33">
+      <c r="M51" s="34">
         <v>0.16</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="34">
         <v>8.24</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <v>8.24</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>8.89</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="34">
         <v>9.14</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="34">
         <v>10.09</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="34">
         <v>12.74</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="34">
         <v>12.13</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="34">
         <v>10.43</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V51" s="34">
         <v>10.49</v>
       </c>
-      <c r="W51" s="33">
+      <c r="W51" s="34">
         <v>10.93</v>
       </c>
-      <c r="X51" s="32"/>
-      <c r="Y51" s="32"/>
-      <c r="Z51" s="32"/>
-      <c r="AA51" s="32"/>
-      <c r="AB51" s="32"/>
+      <c r="X51" s="33"/>
+      <c r="Y51" s="33"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
+      <c r="A52" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
-        <v>509</v>
-      </c>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="33">
+      <c r="A53" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34">
         <v>52.7</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>19.77</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <v>129.3</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>33.23</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>23.38</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>53.17</v>
       </c>
-      <c r="J53" s="32"/>
-      <c r="K53" s="33">
+      <c r="J53" s="33"/>
+      <c r="K53" s="34">
         <v>27.14</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>19.71</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>16.08</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>18.67</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>15.71</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>14.88</v>
       </c>
-      <c r="Q53" s="33">
+      <c r="Q53" s="34">
         <v>12.1</v>
       </c>
-      <c r="R53" s="33">
+      <c r="R53" s="34">
         <v>7.75</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S53" s="34">
         <v>12.44</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <v>22.13</v>
       </c>
-      <c r="U53" s="33">
+      <c r="U53" s="34">
         <v>16.39</v>
       </c>
-      <c r="V53" s="33">
+      <c r="V53" s="34">
         <v>18.53</v>
       </c>
-      <c r="W53" s="32"/>
-      <c r="X53" s="33">
+      <c r="W53" s="33"/>
+      <c r="X53" s="34">
         <v>9.19</v>
       </c>
-      <c r="Y53" s="33">
+      <c r="Y53" s="34">
         <v>26.88</v>
       </c>
-      <c r="Z53" s="33">
+      <c r="Z53" s="34">
         <v>19.51</v>
       </c>
-      <c r="AA53" s="33">
+      <c r="AA53" s="34">
         <v>32.38</v>
       </c>
-      <c r="AB53" s="32"/>
+      <c r="AB53" s="33"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
-        <v>510</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="B54" s="34">
         <v>75.47</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>52.13</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>30.51</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>29.59</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>76.06</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>48.33</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>37.78</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <v>30.66</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>25.73</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>18.54</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>16.6</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>15.17</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>13.3</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>12.47</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>13.22</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="34">
         <v>13.43</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="34">
         <v>14.58</v>
       </c>
-      <c r="S54" s="33">
+      <c r="S54" s="34">
         <v>21.14</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="34">
         <v>21.29</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="34">
         <v>17.54</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="34">
         <v>19.09</v>
       </c>
-      <c r="W54" s="33">
+      <c r="W54" s="34">
         <v>19.34</v>
       </c>
-      <c r="X54" s="32"/>
-      <c r="Y54" s="32"/>
-      <c r="Z54" s="32"/>
-      <c r="AA54" s="32"/>
-      <c r="AB54" s="32"/>
+      <c r="X54" s="33"/>
+      <c r="Y54" s="33"/>
+      <c r="Z54" s="33"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
-        <v>511</v>
-      </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
+      <c r="A55" s="29" t="s">
+        <v>512</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
-        <v>512</v>
-      </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="33">
+      <c r="A56" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34">
         <v>24.07</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>18.79</v>
       </c>
-      <c r="F56" s="32"/>
-      <c r="G56" s="33">
+      <c r="F56" s="33"/>
+      <c r="G56" s="34">
         <v>5.91</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>16.7</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>19.94</v>
       </c>
-      <c r="J56" s="32"/>
-      <c r="K56" s="33">
+      <c r="J56" s="33"/>
+      <c r="K56" s="34">
         <v>20.9</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>20.85</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>15.35</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>18.13</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>14.76</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>14.55</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="Q56" s="34">
         <v>11.88</v>
       </c>
-      <c r="R56" s="33">
+      <c r="R56" s="34">
         <v>8.11</v>
       </c>
-      <c r="S56" s="33">
+      <c r="S56" s="34">
         <v>13.2</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>22.13</v>
       </c>
-      <c r="U56" s="33">
+      <c r="U56" s="34">
         <v>16.39</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="34">
         <v>18.53</v>
       </c>
-      <c r="W56" s="32"/>
-      <c r="X56" s="33">
+      <c r="W56" s="33"/>
+      <c r="X56" s="34">
         <v>11.04</v>
       </c>
-      <c r="Y56" s="33">
+      <c r="Y56" s="34">
         <v>39.71</v>
       </c>
-      <c r="Z56" s="33">
+      <c r="Z56" s="34">
         <v>54.36</v>
       </c>
-      <c r="AA56" s="33">
+      <c r="AA56" s="34">
         <v>51.13</v>
       </c>
-      <c r="AB56" s="32"/>
+      <c r="AB56" s="33"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="B57" s="33">
+      <c r="A57" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="B57" s="34">
         <v>1.39</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>1.45</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>1.47</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>1.42</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.15</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>1.14</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>1.24</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>1.37</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>1.42</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>1.52</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>1.68</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>1.76</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>1.71</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>1.87</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>2.08</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>2.22</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>2.55</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="34">
         <v>2.9</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="34">
         <v>3.12</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="34">
         <v>3.33</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="34">
         <v>3.94</v>
       </c>
-      <c r="W57" s="32"/>
-      <c r="X57" s="32"/>
-      <c r="Y57" s="32"/>
-      <c r="Z57" s="32"/>
-      <c r="AA57" s="32"/>
-      <c r="AB57" s="32"/>
+      <c r="W57" s="33"/>
+      <c r="X57" s="33"/>
+      <c r="Y57" s="33"/>
+      <c r="Z57" s="33"/>
+      <c r="AA57" s="33"/>
+      <c r="AB57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
-        <v>514</v>
-      </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
+      <c r="A58" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
-        <v>515</v>
-      </c>
-      <c r="B59" s="32"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="36">
+      <c r="A59" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="37">
         <v>-0.67</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>0.02</v>
       </c>
-      <c r="F59" s="36">
+      <c r="F59" s="37">
         <v>-2.17</v>
       </c>
-      <c r="G59" s="36">
+      <c r="G59" s="37">
         <v>-0.92</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>0.22</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>0.3</v>
       </c>
-      <c r="J59" s="32"/>
-      <c r="K59" s="36">
+      <c r="J59" s="33"/>
+      <c r="K59" s="37">
         <v>-1.01</v>
       </c>
-      <c r="L59" s="36">
+      <c r="L59" s="37">
         <v>-0.76</v>
       </c>
-      <c r="M59" s="33">
+      <c r="M59" s="34">
         <v>0.66</v>
       </c>
-      <c r="N59" s="36">
+      <c r="N59" s="37">
         <v>-0.67</v>
       </c>
-      <c r="O59" s="36">
+      <c r="O59" s="37">
         <v>-0.71</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>1.21</v>
       </c>
-      <c r="Q59" s="36">
+      <c r="Q59" s="37">
         <v>-1.41</v>
       </c>
-      <c r="R59" s="33">
+      <c r="R59" s="34">
         <v>11.11</v>
       </c>
-      <c r="S59" s="33">
+      <c r="S59" s="34">
         <v>0.21</v>
       </c>
-      <c r="T59" s="36">
+      <c r="T59" s="37">
         <v>-0.89</v>
       </c>
-      <c r="U59" s="33">
+      <c r="U59" s="34">
         <v>0.89</v>
       </c>
-      <c r="V59" s="33">
+      <c r="V59" s="34">
         <v>0.02</v>
       </c>
-      <c r="W59" s="32"/>
-      <c r="X59" s="33">
+      <c r="W59" s="33"/>
+      <c r="X59" s="34">
         <v>0.05</v>
       </c>
-      <c r="Y59" s="36">
+      <c r="Y59" s="37">
         <v>-0.59</v>
       </c>
-      <c r="Z59" s="33">
+      <c r="Z59" s="34">
         <v>0.56</v>
       </c>
-      <c r="AA59" s="36">
+      <c r="AA59" s="37">
         <v>-0.81</v>
       </c>
-      <c r="AB59" s="32"/>
+      <c r="AB59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
-        <v>516</v>
-      </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="33">
+      <c r="A60" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="34">
         <v>3.52</v>
       </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="36">
+      <c r="E60" s="33"/>
+      <c r="F60" s="37">
         <v>-2.71</v>
       </c>
-      <c r="G60" s="36">
+      <c r="G60" s="37">
         <v>-2.55</v>
       </c>
-      <c r="H60" s="36">
+      <c r="H60" s="37">
         <v>-2.28</v>
       </c>
-      <c r="I60" s="36">
+      <c r="I60" s="37">
         <v>-1.24</v>
       </c>
-      <c r="J60" s="32"/>
-      <c r="K60" s="36">
+      <c r="J60" s="33"/>
+      <c r="K60" s="37">
         <v>-1.05</v>
       </c>
-      <c r="L60" s="36">
+      <c r="L60" s="37">
         <v>-1.62</v>
       </c>
-      <c r="M60" s="36">
+      <c r="M60" s="37">
         <v>-2.38</v>
       </c>
-      <c r="N60" s="36">
+      <c r="N60" s="37">
         <v>-1.3</v>
       </c>
-      <c r="O60" s="33">
+      <c r="O60" s="34">
         <v>2.42</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="34">
         <v>3.02</v>
       </c>
-      <c r="Q60" s="33">
+      <c r="Q60" s="34">
         <v>2.44</v>
       </c>
-      <c r="R60" s="32"/>
-      <c r="S60" s="33">
+      <c r="R60" s="33"/>
+      <c r="S60" s="34">
         <v>5.61</v>
       </c>
-      <c r="T60" s="36">
+      <c r="T60" s="37">
         <v>-2.58</v>
       </c>
-      <c r="U60" s="33">
+      <c r="U60" s="34">
         <v>0.95</v>
       </c>
-      <c r="V60" s="33">
+      <c r="V60" s="34">
         <v>13.06</v>
       </c>
-      <c r="W60" s="32"/>
-      <c r="X60" s="32"/>
-      <c r="Y60" s="32"/>
-      <c r="Z60" s="32"/>
-      <c r="AA60" s="32"/>
-      <c r="AB60" s="32"/>
+      <c r="W60" s="33"/>
+      <c r="X60" s="33"/>
+      <c r="Y60" s="33"/>
+      <c r="Z60" s="33"/>
+      <c r="AA60" s="33"/>
+      <c r="AB60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
+      <c r="A61" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
-        <v>518</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="31" t="s">
+        <v>519</v>
+      </c>
+      <c r="B62" s="34">
         <v>0.62</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>0.9</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>1.15</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>1.42</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>0.87</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>0.71</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>0.74</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>0.81</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>1.02</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>1.09</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>1.08</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>1.1</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>1.01</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>1.17</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>1.38</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>1.19</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>0.94</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>1.22</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>1.49</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>1.69</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>1.74</v>
       </c>
-      <c r="W62" s="32"/>
-      <c r="X62" s="33">
+      <c r="W62" s="33"/>
+      <c r="X62" s="34">
         <v>1.45</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>1.94</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="34">
         <v>2.44</v>
       </c>
-      <c r="AA62" s="33">
+      <c r="AA62" s="34">
         <v>3.15</v>
       </c>
-      <c r="AB62" s="32"/>
+      <c r="AB62" s="33"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
-        <v>519</v>
-      </c>
-      <c r="B63" s="33">
+      <c r="A63" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="B63" s="34">
         <v>1.02</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>1.02</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>0.99</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>0.92</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>0.83</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>0.88</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>0.95</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>1.03</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>1.06</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>1.09</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>1.15</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>1.17</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>1.14</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>1.19</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>1.25</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>1.29</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>1.38</v>
       </c>
-      <c r="S63" s="32"/>
-      <c r="T63" s="32"/>
-      <c r="U63" s="32"/>
-      <c r="V63" s="32"/>
-      <c r="W63" s="32"/>
-      <c r="X63" s="32"/>
-      <c r="Y63" s="32"/>
-      <c r="Z63" s="32"/>
-      <c r="AA63" s="32"/>
-      <c r="AB63" s="32"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
+      <c r="W63" s="33"/>
+      <c r="X63" s="33"/>
+      <c r="Y63" s="33"/>
+      <c r="Z63" s="33"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
+      <c r="A64" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
-        <v>521</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B65" s="34">
         <v>8.26</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>11.28</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>10.32</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>10.0</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>12.65</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>4.95</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>7.87</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>11.0</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>18.85</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>10.25</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>9.51</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>0.05</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>8.84</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>10.49</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>9.84</v>
       </c>
-      <c r="Q65" s="33">
+      <c r="Q65" s="34">
         <v>9.61</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="34">
         <v>6.26</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>8.89</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>12.09</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="34">
         <v>12.2</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="34">
         <v>12.15</v>
       </c>
-      <c r="W65" s="32"/>
-      <c r="X65" s="33">
+      <c r="W65" s="33"/>
+      <c r="X65" s="34">
         <v>7.37</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="34">
         <v>10.78</v>
       </c>
-      <c r="Z65" s="33">
+      <c r="Z65" s="34">
         <v>10.95</v>
       </c>
-      <c r="AA65" s="33">
+      <c r="AA65" s="34">
         <v>14.25</v>
       </c>
-      <c r="AB65" s="32"/>
+      <c r="AB65" s="33"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
-        <v>522</v>
-      </c>
-      <c r="B66" s="33">
+      <c r="A66" s="31" t="s">
+        <v>523</v>
+      </c>
+      <c r="B66" s="34">
         <v>10.41</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>9.19</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>8.75</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>8.7</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>9.47</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>9.2</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>10.7</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>0.21</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>0.22</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>0.23</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>0.24</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="34">
         <v>0.24</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="34">
         <v>8.94</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="34">
         <v>8.95</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>9.19</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="34">
         <v>9.57</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="34">
         <v>9.98</v>
       </c>
-      <c r="S66" s="32"/>
-      <c r="T66" s="32"/>
-      <c r="U66" s="32"/>
-      <c r="V66" s="32"/>
-      <c r="W66" s="32"/>
-      <c r="X66" s="32"/>
-      <c r="Y66" s="32"/>
-      <c r="Z66" s="32"/>
-      <c r="AA66" s="32"/>
-      <c r="AB66" s="32"/>
+      <c r="S66" s="33"/>
+      <c r="T66" s="33"/>
+      <c r="U66" s="33"/>
+      <c r="V66" s="33"/>
+      <c r="W66" s="33"/>
+      <c r="X66" s="33"/>
+      <c r="Y66" s="33"/>
+      <c r="Z66" s="33"/>
+      <c r="AA66" s="33"/>
+      <c r="AB66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
+      <c r="A67" s="29" t="s">
+        <v>524</v>
+      </c>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="B68" s="34">
         <v>5.86</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>9.64</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="33">
+      <c r="D68" s="33"/>
+      <c r="E68" s="34">
         <v>17.14</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>5.36</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>7.53</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>29.02</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>10.71</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>9.95</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>19.51</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="34">
         <v>13.59</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>20.53</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>11.68</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>21.61</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>28.61</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>11.01</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>35.79</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>15.87</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>33.86</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>27.42</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>33.1</v>
       </c>
-      <c r="W68" s="32"/>
-      <c r="X68" s="33">
+      <c r="W68" s="33"/>
+      <c r="X68" s="34">
         <v>7.57</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>152.67</v>
       </c>
-      <c r="Z68" s="33">
+      <c r="Z68" s="34">
         <v>26.02</v>
       </c>
-      <c r="AA68" s="33">
+      <c r="AA68" s="34">
         <v>32.25</v>
       </c>
-      <c r="AB68" s="32"/>
+      <c r="AB68" s="33"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
-        <v>525</v>
-      </c>
-      <c r="B69" s="33">
+      <c r="A69" s="31" t="s">
+        <v>526</v>
+      </c>
+      <c r="B69" s="34">
         <v>13.25</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>13.5</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>15.61</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>10.45</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>8.99</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>12.38</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>14.08</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>14.07</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>14.11</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>16.52</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>17.74</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>16.88</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>17.65</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>19.14</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>20.63</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="34">
         <v>20.33</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>26.61</v>
       </c>
-      <c r="S69" s="32"/>
-      <c r="T69" s="32"/>
-      <c r="U69" s="32"/>
-      <c r="V69" s="32"/>
-      <c r="W69" s="32"/>
-      <c r="X69" s="32"/>
-      <c r="Y69" s="32"/>
-      <c r="Z69" s="32"/>
-      <c r="AA69" s="32"/>
-      <c r="AB69" s="32"/>
+      <c r="S69" s="33"/>
+      <c r="T69" s="33"/>
+      <c r="U69" s="33"/>
+      <c r="V69" s="33"/>
+      <c r="W69" s="33"/>
+      <c r="X69" s="33"/>
+      <c r="Y69" s="33"/>
+      <c r="Z69" s="33"/>
+      <c r="AA69" s="33"/>
+      <c r="AB69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
-        <v>526</v>
-      </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
-      <c r="AA70" s="29"/>
-      <c r="AB70" s="29"/>
+      <c r="A70" s="29" t="s">
+        <v>527</v>
+      </c>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
-        <v>527</v>
-      </c>
-      <c r="B71" s="33">
+      <c r="A71" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="B71" s="34">
         <v>7.15</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="34">
         <v>17.89</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="33">
+      <c r="D71" s="33"/>
+      <c r="E71" s="34">
         <v>40.6</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="34">
         <v>6.07</v>
       </c>
-      <c r="G71" s="33">
+      <c r="G71" s="34">
         <v>9.61</v>
       </c>
-      <c r="H71" s="31">
+      <c r="H71" s="32">
         <v>648.17</v>
       </c>
-      <c r="I71" s="33">
+      <c r="I71" s="34">
         <v>15.62</v>
       </c>
-      <c r="J71" s="33">
+      <c r="J71" s="34">
         <v>14.52</v>
       </c>
-      <c r="K71" s="33">
+      <c r="K71" s="34">
         <v>46.82</v>
       </c>
-      <c r="L71" s="33">
+      <c r="L71" s="34">
         <v>13.59</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="34">
         <v>67.28</v>
       </c>
-      <c r="N71" s="33">
+      <c r="N71" s="34">
         <v>16.82</v>
       </c>
-      <c r="O71" s="33">
+      <c r="O71" s="34">
         <v>48.29</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="34">
         <v>54.7</v>
       </c>
-      <c r="Q71" s="33">
+      <c r="Q71" s="34">
         <v>15.62</v>
       </c>
-      <c r="R71" s="32"/>
-      <c r="S71" s="33">
+      <c r="R71" s="33"/>
+      <c r="S71" s="34">
         <v>25.89</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>120.92</v>
       </c>
-      <c r="U71" s="33">
+      <c r="U71" s="34">
         <v>52.66</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="32">
         <v>103.86</v>
       </c>
-      <c r="W71" s="32"/>
-      <c r="X71" s="33">
+      <c r="W71" s="33"/>
+      <c r="X71" s="34">
         <v>9.05</v>
       </c>
-      <c r="Y71" s="32"/>
-      <c r="Z71" s="33">
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="34">
         <v>38.56</v>
       </c>
-      <c r="AA71" s="33">
+      <c r="AA71" s="34">
         <v>45.48</v>
       </c>
-      <c r="AB71" s="32"/>
+      <c r="AB71" s="33"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
-        <v>528</v>
-      </c>
-      <c r="B72" s="33">
+      <c r="A72" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="B72" s="34">
         <v>24.18</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="34">
         <v>24.75</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>30.73</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="34">
         <v>15.21</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="34">
         <v>12.15</v>
       </c>
-      <c r="G72" s="33">
+      <c r="G72" s="34">
         <v>19.9</v>
       </c>
-      <c r="H72" s="33">
+      <c r="H72" s="34">
         <v>21.1</v>
       </c>
-      <c r="I72" s="33">
+      <c r="I72" s="34">
         <v>21.55</v>
       </c>
-      <c r="J72" s="33">
+      <c r="J72" s="34">
         <v>21.48</v>
       </c>
-      <c r="K72" s="33">
+      <c r="K72" s="34">
         <v>26.89</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="34">
         <v>27.93</v>
       </c>
-      <c r="M72" s="33">
+      <c r="M72" s="34">
         <v>29.62</v>
       </c>
-      <c r="N72" s="33">
+      <c r="N72" s="34">
         <v>31.13</v>
       </c>
-      <c r="O72" s="33">
+      <c r="O72" s="34">
         <v>35.64</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="34">
         <v>39.64</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="34">
         <v>39.1</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="34">
         <v>65.89</v>
       </c>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="32"/>
-      <c r="Y72" s="32"/>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
+      <c r="S72" s="33"/>
+      <c r="T72" s="33"/>
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
+      <c r="W72" s="33"/>
+      <c r="X72" s="33"/>
+      <c r="Y72" s="33"/>
+      <c r="Z72" s="33"/>
+      <c r="AA72" s="33"/>
+      <c r="AB72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
